--- a/docs/blood-of-icetear-cards.xlsx
+++ b/docs/blood-of-icetear-cards.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Rarities" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Characters'!$A$1:$L$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Characters'!$A$1:$L$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Spells'!$A$1:$L$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Rarities'!$A$1:$F$7</definedName>
   </definedNames>
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -571,7 +571,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.077</t>
+          <t>N0.01.BOI.080</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.065</t>
+          <t>N0.01.BOI.068</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.073</t>
+          <t>N0.01.BOI.076</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.064</t>
+          <t>N0.01.BOI.067</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.075</t>
+          <t>N0.01.BOI.078</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.050</t>
+          <t>N0.01.BOI.053</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -987,7 +987,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.070</t>
+          <t>N0.01.BOI.073</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1032,19 +1032,19 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>tylon-leviathan.webp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.023</t>
+          <t>N0.01.BOI.027</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Antharaiel Whitewing</t>
+          <t>Adamas, First King of Men</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>High Elf Lord</t>
+          <t>Human Lord</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1073,30 +1073,34 @@
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>When Antharaiel Whitewing enters the arena, return a spell from your graveyard to your hand.</t>
+          <t>Your Human characters strike with +4 Power. While Adamas is in the arena, your Citadel Mastery cannot fall by more than 5 in a single turn.</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Ellescand, Crown</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr"/>
+          <t>Humanity, Crown</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Adamas, Father of Humanity</t>
+        </is>
+      </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>antharaiel-whitewing.webp</t>
+          <t>adamas-first-king.webp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.072</t>
+          <t>N0.01.BOI.023</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>The Morrigan’s Avatar</t>
+          <t>Antharaiel Whitewing</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1106,7 +1110,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Ancient Avatar</t>
+          <t>High Elf Lord</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1125,30 +1129,30 @@
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>When The Morrigan’s Avatar enters the arena, return a Legendary character from your graveyard and give it +13 Power while the Avatar remains.</t>
+          <t>When Antharaiel Whitewing enters the arena, return a spell from your graveyard to your hand.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Divine, Avatar</t>
+          <t>Ellescand, Crown</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>morrigan.jpg</t>
+          <t>antharaiel-whitewing.webp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.021</t>
+          <t>N0.01.BOI.051</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Tiamel, First Queen of the Elu-Dragar</t>
+          <t>King Koschei, the Berserker King of Golskull</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1158,7 +1162,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Dragon Elf Lord</t>
+          <t>Zombie Lord</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1177,30 +1181,34 @@
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>When Tiamel enters the arena, deal 6 damage to every enemy character.</t>
+          <t>Quick Attack. When a friendly Undead dies, King Koschei gains 4 Power. When King Koschei dies, return him to your hand.</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dragar, Crown</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
+          <t>Undead, Crown</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Koschei, the Zombie King</t>
+        </is>
+      </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>tiamel.webp</t>
+          <t>king-koschei.webp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.063</t>
+          <t>N0.01.BOI.075</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>World Sage Nilream, The White Dragon</t>
+          <t>The Morrigan’s Avatar</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1210,7 +1218,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Elder Dragon</t>
+          <t>Ancient Avatar</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1229,30 +1237,30 @@
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>When World Sage Nilream enters the arena, halve the Power of every enemy character.</t>
+          <t>When The Morrigan’s Avatar enters the arena, return a Legendary character from your graveyard and give it +13 Power while the Avatar remains.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Dragon, Sage</t>
+          <t>Divine, Avatar</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>morrigan.jpg</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.076</t>
+          <t>N0.01.BOI.021</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Grand Liger, The Guardian</t>
+          <t>Tiamel, First Queen of the Elu-Dragar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1262,7 +1270,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Divine Soul</t>
+          <t>Dragon Elf Lord</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1271,7 +1279,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>10</v>
@@ -1281,30 +1289,30 @@
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Gains +2 Power for every other character in the arena.</t>
+          <t>When Tiamel enters the arena, deal 6 damage to every enemy character.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Divine</t>
+          <t>Elu-Dragar, Crown</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>avalonus.jpg</t>
+          <t>tiamel.webp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.30</t>
+          <t>N0.01.BOI.066</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Sinbad-Sinodess, The Pirate King</t>
+          <t>World Sage Nilream, The White Dragon</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1314,7 +1322,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Chosen Human</t>
+          <t>Elder Dragon</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1323,7 +1331,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>10</v>
@@ -1333,30 +1341,30 @@
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>When Sinbad-Sinodess enters the arena, exchange 2 of your characters for 2 of your opponent’s.</t>
+          <t>When World Sage Nilream enters the arena, halve the Power of every enemy character.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Sinodess, Crown</t>
+          <t>Dragon, Sage</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>sinbad-sinodess.jpg</t>
+          <t>world-sage-nilream.webp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.25</t>
+          <t>N0.01.BOI.079</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Susanna Bruhneville, Great Witch of the North</t>
+          <t>Grand Liger, The Guardian</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1366,7 +1374,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Ancient Spirit</t>
+          <t>Divine Soul</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -1385,30 +1393,30 @@
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
+          <t>Gains +2 Power for every other character in the arena.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Witch</t>
+          <t>Divine</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>susanna-bruhneville.webp</t>
+          <t>avalonus.jpg</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.22</t>
+          <t>N0.01.LAH.30</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Helena Katsunra, Great Witch of the East</t>
+          <t>Sinbad-Sinodess, The Pirate King</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1418,49 +1426,49 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>Ascendant</t>
+          <t>Chosen Human</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Mythical</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
+          <t>When Sinbad-Sinodess enters the arena, exchange 2 of your characters for 2 of your opponent’s.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Witch</t>
+          <t>Sinodess, Crown</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>sinbad-sinodess.jpg</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.071</t>
+          <t>N0.01.LAH.25</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Lucifial’s Avatar, The Whisperer</t>
+          <t>Susanna Bruhneville, Great Witch of the North</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1470,49 +1478,49 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Titanic Avatar</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Ascendant</t>
+          <t>Ancient Spirit</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Mythical</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>When The Whisperer enters the arena, take a character from your opponent’s hand.</t>
+          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Devil, Avatar</t>
+          <t>Witch</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lucifials-avatar.jpg</t>
+          <t>susanna-bruhneville.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.24</t>
+          <t>N0.01.LAH.22</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Melissra Orscina, Great Witch of the South</t>
+          <t>Helena Katsunra, Great Witch of the East</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1522,7 +1530,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Elder Vampire</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1546,25 +1554,25 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Witch, Vampire</t>
+          <t>Witch</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>helena-katsunra.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.23</t>
+          <t>N0.01.BOI.074</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Morrina Penfyre, Great Witch of the West</t>
+          <t>Lucifial’s Avatar, The Whisperer</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1574,7 +1582,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Titanic Avatar</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -1593,30 +1601,30 @@
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
+          <t>When The Whisperer enters the arena, take a character from your opponent’s hand.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Witch</t>
+          <t>Devil, Avatar</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>lucifials-avatar.jpg</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.26</t>
+          <t>N0.01.LAH.24</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Seneal Icetear</t>
+          <t>Melissra Orscina, Great Witch of the South</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1626,7 +1634,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Elder Vampire</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -1650,25 +1658,25 @@
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Icetear, Witch</t>
+          <t>Witch, Vampire</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>melissra-orscina.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.027</t>
+          <t>N0.01.LAH.23</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Adamas, Father of Humanity</t>
+          <t>Morrina Penfyre, Great Witch of the West</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1678,7 +1686,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Human Lord</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -1687,7 +1695,7 @@
         </is>
       </c>
       <c r="F23" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>9</v>
@@ -1697,30 +1705,30 @@
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>While Adamas is in the arena, your Citadel Mastery cannot fall by more than 10 in a single turn.</t>
+          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Humanity, Crown</t>
+          <t>Witch, Penfyre</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>adamas.webp</t>
+          <t>morrina-penfyre.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.062</t>
+          <t>N0.01.LAH.26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Barlgowrath</t>
+          <t>Seneal Icetear, Witch Queen of the North</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1730,7 +1738,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Ancient Beast</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -1739,7 +1747,7 @@
         </is>
       </c>
       <c r="F24" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>9</v>
@@ -1749,30 +1757,30 @@
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>When Barlgowrath strikes a character, he strikes every character beside it as well.</t>
+          <t>Halve the Power of every enemy character for two of your opponent’s turns.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Icetear, Witch</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>spider-horror.webp</t>
+          <t>seneal-icetear.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.020</t>
+          <t>N0.01.BOI.028</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Darklord Anthurian</t>
+          <t>Adamas, Father of Humanity</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1782,7 +1790,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Half Elf Lord</t>
+          <t>Human Lord</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -1801,30 +1809,34 @@
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>When Darklord Anthurian enters the arena, destroy your own weakest character and add its Power to his.</t>
+          <t>While Adamas is in the arena, your Citadel Mastery cannot fall by more than 10 in a single turn.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dues, Fallen</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
+          <t>Humanity, Crown</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Adamas, First King of Men</t>
+        </is>
+      </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>adamas.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.030</t>
+          <t>N0.01.BOI.065</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Caligula, King of Domination</t>
+          <t>Barlgowrath</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1834,7 +1846,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood</t>
+          <t>Ancient Beast</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -1843,40 +1855,40 @@
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>When Caligula enters the arena, take control of an enemy Rare or lower character for the rest of the match.</t>
+          <t>When Barlgowrath strikes a character, he strikes every character beside it as well.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood, Crown</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>caligula.jpg</t>
+          <t>spider-horror.webp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.06</t>
+          <t>N0.01.BOI.020</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Hannarial Icetear, Captain of the Red Rangers</t>
+          <t>Darklord Anthurian Bloodwing</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1886,7 +1898,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Half Elf Lord</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -1895,7 +1907,7 @@
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>9</v>
@@ -1905,34 +1917,30 @@
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>When Hannarial Icetear enters the arena, summon 2 Red Rangers Squad Leaders to your side of the arena.</t>
+          <t>When Darklord Anthurian enters the arena, destroy your own weakest character and add its Power to his.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Icetear</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Hannarial Icetear</t>
-        </is>
-      </c>
+          <t>Elu-Dues, Fallen</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>hannarial.webp</t>
+          <t>darklord-anthurian.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.019</t>
+          <t>N0.01.BOI.031</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>King Gilgamesh</t>
+          <t>Caligula, King of Domination</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1942,7 +1950,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Half Elf Lord</t>
+          <t>Gods Blood</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -1954,37 +1962,37 @@
         <v>22</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Gilgamesh dies, deal his Power to the enemy Citadel.</t>
+          <t>When Caligula enters the arena, take control of an enemy Rare or lower character for the rest of the match.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dues, Crown</t>
+          <t>Gods Blood, Crown</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>gilgamesh.webp</t>
+          <t>caligula.jpg</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.049</t>
+          <t>N0.01.LAH.06</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Koschei, the Zombie King</t>
+          <t>Hannarial Icetear, Captain of the Red Rangers</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1994,7 +2002,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Zombie Lord</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2013,30 +2021,34 @@
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When a friendly Undead dies, Koschei gains 2 Power.</t>
+          <t>When Hannarial Icetear enters the arena, summon 2 Red Rangers Squad Leaders to your side of the arena.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Undead, Crown</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
+          <t>Red Rangers, Icetear</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Hannarial Icetear</t>
+        </is>
+      </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>hannarial.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.061</t>
+          <t>N0.01.BOI.019</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Leonarr</t>
+          <t>King Gilgamesh</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2046,7 +2058,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Beast King</t>
+          <t>Half Elf Lord</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -2065,40 +2077,40 @@
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Your other Beast characters strike with +2 Power.</t>
+          <t>Quick Attack. When Gilgamesh dies, deal his Power to the enemy Citadel.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Beast, Crown</t>
+          <t>Elu-Dues, Crown</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>gilgamesh.webp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.069</t>
+          <t>N0.01.BOI.052</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Tylon (Spirit Awakened)</t>
+          <t>Koschei, the Zombie King</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
+          <t>Zombie Lord</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -2117,30 +2129,34 @@
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Tylon (Spirit Awakened) dies, return it to your hand.</t>
+          <t>Quick Attack. When a friendly Undead dies, Koschei gains 2 Power.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Beast, Awakened</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
+          <t>Undead, Crown</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>King Koschei, the Berserker King of Golskull</t>
+        </is>
+      </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>koschei.webp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.039</t>
+          <t>N0.01.BOI.064</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Warlord Wufgarr</t>
+          <t>Leonarr</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2150,7 +2166,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Orc Lord</t>
+          <t>Beast King</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -2169,12 +2185,12 @@
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Warlord Wufgarr enters the arena, summon 2 Orc Raiders.</t>
+          <t>Your other Beast characters strike with +2 Power.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Orc, Warband</t>
+          <t>Beast, Crown</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
@@ -2187,22 +2203,22 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.16</t>
+          <t>N0.01.BOI.072</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Anthurian Icetear, Vice Captain of the Red Rangers</t>
+          <t>Tylon (Spirit Awakened)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -2211,40 +2227,40 @@
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>When Anthurian Icetear enters the arena, summon 2 Red Rangers Squad Leaders to your side of the arena.</t>
+          <t>Quick Attack. When Tylon (Spirit Awakened) dies, return it to your hand.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Icetear</t>
+          <t>Beast, Awakened</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>anthuriun.webp</t>
+          <t>tylon-spirit-awakened.webp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.043</t>
+          <t>N0.01.BOI.041</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Archmagi Treantan</t>
+          <t>Warlord Wufgarr</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2254,7 +2270,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Treant Wizard</t>
+          <t>Orc Lord</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -2263,40 +2279,40 @@
         </is>
       </c>
       <c r="F34" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. At the end of your turn, Archmagi Treantan gains 2 Power.</t>
+          <t>Quick Attack. When Warlord Wufgarr enters the arena, summon 2 Orc Raiders.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Archmagi, Treant</t>
+          <t>Orc, Warband</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>warlord-wufgarr.webp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.031</t>
+          <t>N0.01.LAH.16</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Godrian Greyhide, Realm Commander</t>
+          <t>Anthurian Icetear, Vice Captain of the Red Rangers</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2306,7 +2322,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Human Lord</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -2318,37 +2334,37 @@
         <v>21</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Your other Human characters gain +3 Power.</t>
+          <t>When Anthurian Icetear enters the arena, summon 2 Red Rangers Squad Leaders to your side of the arena.</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Red Rangers, Icetear</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>godrian-greyhide.jpg</t>
+          <t>anthuriun.webp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.018</t>
+          <t>N0.01.BOI.045</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Karscyll, Sixth Queen of Elu-Dragar</t>
+          <t>Archmagi Treantan</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2358,7 +2374,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Dragon Elf Lord</t>
+          <t>Treant Wizard</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -2370,19 +2386,19 @@
         <v>21</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Quick Attack. At the end of your turn, Archmagi Treantan gains 2 Power.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dragar, Crown</t>
+          <t>Archmagi, Treant</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr"/>
@@ -2395,12 +2411,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.060</t>
+          <t>N0.01.BOI.032</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Lycanor</t>
+          <t>Godrian Greyhide, Realm Commander</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2410,7 +2426,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Beast King</t>
+          <t>Human Lord</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -2429,40 +2445,40 @@
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Lycanor enters the arena, summon 2 Wolves.</t>
+          <t>Your other Human characters gain +3 Power.</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Beast, Wolf, Crown</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>godrian-greyhide.webp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.048</t>
+          <t>N0.01.BOI.018</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Wraith Knight</t>
+          <t>Karscyll, 3rd Queen of Elu-Dragar</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Dragon Elf Lord</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -2474,37 +2490,37 @@
         <v>21</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>Cannot be destroyed by a spell. When Wraith Knight dies, exile it.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Undead, Knight</t>
+          <t>Elu-Dragar, Crown</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>winged-lich.webp</t>
+          <t>karscyll.webp</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.036</t>
+          <t>N0.01.BOI.063</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Zhou Ying, Phoenix General</t>
+          <t>Lycanor</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2514,7 +2530,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Human Lord</t>
+          <t>Beast King</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -2533,12 +2549,12 @@
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>When Zhou Ying dies, return her to your hand.</t>
+          <t>Quick Attack. When Lycanor enters the arena, summon 2 Wolves.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Crown</t>
+          <t>Beast, Wolf, Crown</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
@@ -2551,22 +2567,22 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.042</t>
+          <t>N0.01.BOI.050</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Archmagi Geof</t>
+          <t>Wraith Knight</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Dwarf Wizard</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -2575,7 +2591,7 @@
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>8</v>
@@ -2585,30 +2601,30 @@
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Archmagi Geof enters the arena, give a friendly character +5 Power.</t>
+          <t>Cannot be destroyed by a spell. When Wraith Knight dies, exile it.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Archmagi, Dwarf</t>
+          <t>Undead, Knight</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>winged-lich.webp</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.044</t>
+          <t>N0.01.BOI.038</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Archmagi Serra</t>
+          <t>Zhou Ying, Phoenix General</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2618,7 +2634,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>High Elf Wizard</t>
+          <t>Human Lord</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -2627,7 +2643,7 @@
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>8</v>
@@ -2637,30 +2653,30 @@
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Archmagi Serra enters the arena, return a spell from your graveyard to your hand.</t>
+          <t>When Zhou Ying dies, return her to your hand.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Archmagi</t>
+          <t>Crown</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>zhou-ying.webp</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.017</t>
+          <t>N0.01.BOI.044</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Avalon, Queen of Elu-Hsal</t>
+          <t>Archmagi Geof</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2670,7 +2686,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Soul Elf Lord</t>
+          <t>Dwarf Wizard</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -2689,12 +2705,12 @@
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Avalon enters the arena, return a character from your graveyard to your hand.</t>
+          <t>Quick Attack. When Archmagi Geof enters the arena, give a friendly character +5 Power.</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Elu-Hsal, Crown</t>
+          <t>Archmagi, Dwarf</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr"/>
@@ -2707,12 +2723,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.028</t>
+          <t>N0.01.BOI.046</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>King Solomon, King of Ambition</t>
+          <t>Archmagi Serra</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2722,7 +2738,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood</t>
+          <t>High Elf Wizard</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -2741,30 +2757,30 @@
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>When King Solomon enters the arena, take a card at random from your opponent’s hand.</t>
+          <t>Quick Attack. When Archmagi Serra enters the arena, return a spell from your graveyard to your hand.</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood, Crown</t>
+          <t>Archmagi</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>solomon.jpg</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.037</t>
+          <t>N0.01.BOI.017</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Mordred, The Broken</t>
+          <t>Avalon, Queen of Elu-Hsal</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2774,7 +2790,7 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Human Druid</t>
+          <t>Soul Elf Lord</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -2793,12 +2809,12 @@
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>When Mordred strikes, he loses 2 Power and the struck character loses 2 more.</t>
+          <t>Quick Attack. When Avalon enters the arena, return a character from your graveyard to your hand.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Fallen, Druid</t>
+          <t>Elu-Hsal, Crown</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr"/>
@@ -2811,22 +2827,22 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.089</t>
+          <t>N0.01.BOI.029</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Norgod Jarl</t>
+          <t>King Solomon, King of Ambition</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Norgods</t>
+          <t>Gods Blood</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -2845,30 +2861,30 @@
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Your other Norgod characters have Quick Attack.</t>
+          <t>When King Solomon enters the arena, take a card at random from your opponent’s hand.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Norgods, Crown</t>
+          <t>Gods Blood, Crown</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>solomon.jpg</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.08</t>
+          <t>N0.01.BOI.039</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Solenyra Gravespine</t>
+          <t>Mordred, The Broken</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2878,7 +2894,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human Druid</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -2897,40 +2913,40 @@
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>When Solenyra Gravespine enters the arena, exile 2 Rare or lower characters, or exile 1 Epic or higher character.</t>
+          <t>When Mordred strikes, he loses 2 Power and the struck character loses 2 more.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Gravespine</t>
+          <t>Fallen, Druid</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>mordred.webp</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.041</t>
+          <t>N0.01.BOI.092</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Archmagi Vault</t>
+          <t>Norgod Jarl</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Human Wizard</t>
+          <t>Norgods</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -2939,7 +2955,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>8</v>
@@ -2949,12 +2965,12 @@
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. Your spells cost 1 less.</t>
+          <t>Your other Norgod characters have Quick Attack.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Archmagi</t>
+          <t>Norgods, Crown</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr"/>
@@ -2967,12 +2983,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.047</t>
+          <t>N0.01.LAH.08</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Miss Crowly</t>
+          <t>Solenyra Gravespine, High-Warden of the Red Rangers</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2982,7 +2998,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Ancient Spirit</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -2991,7 +3007,7 @@
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>8</v>
@@ -3001,30 +3017,30 @@
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>When Miss Crowly enters the arena, an enemy character loses 10 Power for two turns.</t>
+          <t>When Solenyra Gravespine enters the arena, exile 2 Rare or lower characters, or exile 1 Epic or higher character.</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Red Rangers, Gravespine</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>solenyra-gravespine.webp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.035</t>
+          <t>N0.01.BOI.043</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Zhuge Guan, Dragon Strategist</t>
+          <t>Archmagi Vault</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -3034,7 +3050,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Human Lord</t>
+          <t>Human Wizard</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -3053,12 +3069,12 @@
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>When Zhuge Guan enters the arena, look at your opponent’s hand and take a spell from it.</t>
+          <t>Quick Attack. Your spells cost 1 less.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Crown, Strategist</t>
+          <t>Archmagi</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr"/>
@@ -3071,12 +3087,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.10</t>
+          <t>N0.01.BOI.049</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Duke Lycareon Tyberious</t>
+          <t>Miss Crowly</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -3086,16 +3102,16 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
-        </is>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Ancient Spirit</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Ascendant</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G50" s="2" t="n">
         <v>8</v>
@@ -3105,30 +3121,30 @@
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>When Duke Lycareon enters the arena, destroy one Epic, one Rare and one Uncommon character.</t>
+          <t>When Miss Crowly enters the arena, an enemy character loses 10 Power for two turns.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Wolfsbane, Assassin</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>miss-crowly.webp</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.09</t>
+          <t>N0.01.BOI.036</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Shaedra Nyxthorn</t>
+          <t>Prince Arthur Penfyre</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -3138,101 +3154,101 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Ascendant</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>When Shaedra Nyxthorn enters the arena, summon 2 Red Rangers to your side of the arena.</t>
+          <t>When Prince Arthur Penfyre enters the arena, summon 2 Knights to your side of the arena.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Nyxthorn</t>
+          <t>Lionheart, Penfyre, Knight</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>shaedra-nyxthorn.jpg</t>
+          <t>prince-arthur-penfyre.webp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.068</t>
+          <t>N0.01.BOI.037</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Tylon (Awakened)</t>
+          <t>Zhuge Guan, Dragon Strategist</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>Epic</t>
+          <t>Human Lord</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Ascendant</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. Cannot be destroyed by a spell.</t>
+          <t>When Zhuge Guan enters the arena, look at your opponent’s hand and take a spell from it.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Beast, Awakened</t>
+          <t>Crown, Strategist</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>zhuge-guan.webp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.15</t>
+          <t>N0.01.LAH.10</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Amvala Nyxthorn</t>
+          <t>Duke Lycareon Tyberious</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3242,7 +3258,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
@@ -3251,22 +3267,22 @@
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Counts as a Red Ranger. When Amvala Nyxthorn dies, return her to your side of the arena at the start of your opponent’s turn. If she dies again, exile her.</t>
+          <t>When Duke Lycareon enters the arena, destroy one Epic, one Rare and one Uncommon character.</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Nyxthorn</t>
+          <t>Wolfsbane, Assassin</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr"/>
@@ -3279,12 +3295,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.026</t>
+          <t>N0.01.LAH.09</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Cainan, First Son of Humanity</t>
+          <t>Shaedra Nyxthorn</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3294,7 +3310,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
@@ -3303,7 +3319,7 @@
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>6</v>
@@ -3313,30 +3329,30 @@
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>When Cainan enters the arena, destroy a friendly character. Cainan gains half its Power.</t>
+          <t>When Shaedra Nyxthorn enters the arena, summon 2 Red Rangers to your side of the arena.</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Red Rangers, Nyxthorn</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>cainan.webp</t>
+          <t>shaedra-nyxthorn.jpg</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.085</t>
+          <t>N0.01.BOI.071</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>High Inquisitor</t>
+          <t>Tylon (Awakened)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3346,7 +3362,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
@@ -3355,7 +3371,7 @@
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>7</v>
@@ -3365,30 +3381,30 @@
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>When High Inquisitor enters the arena, exile every card in both graveyards.</t>
+          <t>Quick Attack. Cannot be destroyed by a spell.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Inquisition</t>
+          <t>Beast, Awakened</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>tylon-awakened.webp</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.014</t>
+          <t>N0.01.LAH.15</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Sederous Lionheart, King of Scraps</t>
+          <t>Amvala Nyxthorn</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3398,7 +3414,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Half Elf Lord</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
@@ -3410,37 +3426,37 @@
         <v>16</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Costs 1 less for each character in your graveyard, to a minimum of 3.</t>
+          <t>Counts as a Red Ranger. When Amvala Nyxthorn dies, return her to your side of the arena at the start of your opponent’s turn. If she dies again, exile her.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Lionheart, Crown</t>
+          <t>Red Rangers, Nyxthorn</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>sederous.webp</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.059</t>
+          <t>N0.01.BOI.026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Winter, Ghosthowl</t>
+          <t>Cainan, First Son of Humanity</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3450,7 +3466,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Beastling</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
@@ -3462,37 +3478,37 @@
         <v>16</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>When Winter enters the arena, summon 2 Wolves to your side of the arena.</t>
+          <t>When Cainan enters the arena, destroy a friendly character. Cainan gains half its Power.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Beast, Wolf</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>cainan.webp</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.058</t>
+          <t>N0.01.BOI.088</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Fallen Lycaron</t>
+          <t>High Inquisitor</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3502,7 +3518,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Beastling</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3511,22 +3527,22 @@
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>When Fallen Lycaron kills a character, he gains 3 Power.</t>
+          <t>When High Inquisitor enters the arena, exile every card in both graveyards.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Beast, Fallen</t>
+          <t>Inquisition</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr"/>
@@ -3539,12 +3555,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.029</t>
+          <t>N0.01.BOI.014</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Lazarus, High Councilor</t>
+          <t>Sederous Lionheart, King of Scraps</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3554,7 +3570,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood</t>
+          <t>Half Elf Lord</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
@@ -3563,7 +3579,7 @@
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>6</v>
@@ -3573,40 +3589,40 @@
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Cannot be struck while another friendly character is in the arena.</t>
+          <t>Costs 1 less for each character in your graveyard, to a minimum of 3.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood, Shadow</t>
+          <t>Lionheart, Crown</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lazarus.jpg</t>
+          <t>sederous.webp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.084</t>
+          <t>N0.01.BOI.062</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Matron of the Moon</t>
+          <t>Winter, Ghosthowl</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Human Knight</t>
+          <t>Beastling</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
@@ -3615,40 +3631,40 @@
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>Your other Knight Sisterhood characters gain +2 Power.</t>
+          <t>When Winter enters the arena, summon 2 Wolves to your side of the arena.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Knight Sisterhood, Knight</t>
+          <t>Beast, Wolf</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>winter-ghosthowl.webp</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.02</t>
+          <t>N0.01.BOI.015</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Nyrial Dagrhan</t>
+          <t>Anna, the White Witch</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3658,7 +3674,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Dragon Elf Lord</t>
+          <t>Half Elf</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
@@ -3677,40 +3693,40 @@
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>May strike twice in the same turn. Loses 5 Power if she strikes a second time.</t>
+          <t>When Anna enters the arena, an enemy character cannot strike for two turns.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dragar</t>
+          <t>Elu-Dues, Witch</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>anna-white-witch.webp</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.015</t>
+          <t>N0.01.BOI.061</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Princess Anna, the White Witch</t>
+          <t>Fallen Lycaron</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Half Elf</t>
+          <t>Beastling</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
@@ -3722,19 +3738,19 @@
         <v>15</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>When Princess Anna enters the arena, an enemy character cannot strike for two turns.</t>
+          <t>When Fallen Lycaron kills a character, he gains 3 Power.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dues, Witch</t>
+          <t>Beast, Fallen</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
@@ -3747,22 +3763,22 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.067</t>
+          <t>N0.01.BOI.030</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Tylon (Corrupted)</t>
+          <t>Lazarus, High Councilor</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
+          <t>Gods Blood</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
@@ -3774,47 +3790,47 @@
         <v>15</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. When Tylon (Corrupted) kills a character, it gains 2 Power.</t>
+          <t>Cannot be struck while another friendly character is in the arena.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Beast, Corrupted</t>
+          <t>Gods Blood, Shadow</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>lazarus.jpg</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.025</t>
+          <t>N0.01.BOI.087</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Abel, Second Son of Humanity</t>
+          <t>Matron of the Moon</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human Knight</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
@@ -3823,40 +3839,40 @@
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>When Abel dies, a friendly character gains +6 Power. Exile Abel.</t>
+          <t>Your other Knight Sisterhood characters gain +2 Power.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Knight Sisterhood, Knight</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>abel.webp</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.012</t>
+          <t>N0.01.LAH.02</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Glorfarsall Elysium</t>
+          <t>Nyrial Dagrhan, Princess of the Elu-Draghar</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3866,7 +3882,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Dragon Elf Lord</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -3875,40 +3891,40 @@
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I65" s="4" t="inlineStr">
         <is>
-          <t>Your other characters strike with +1 Power.</t>
+          <t>May strike twice in the same turn. Loses 5 Power if she strikes a second time.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Sacred Order</t>
+          <t>Elu-Dragar</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>glorfarsall.webp</t>
+          <t>nyrial-dagrhan.webp</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.088</t>
+          <t>N0.01.BOI.070</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Norgod Reaver</t>
+          <t>Tylon (Corrupted)</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3918,7 +3934,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Norgods</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -3927,7 +3943,7 @@
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>5</v>
@@ -3937,35 +3953,35 @@
       </c>
       <c r="I66" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack. Strikes with +3 Power while your Citadel Mastery is below 50.</t>
+          <t>Quick Attack. When Tylon (Corrupted) kills a character, it gains 2 Power.</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Norgods</t>
+          <t>Beast, Corrupted</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>tylon-corrupted.webp</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.083</t>
+          <t>N0.01.BOI.025</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Slayer Captain</t>
+          <t>Abel, Second Son of Humanity</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3982,47 +3998,47 @@
         <v>14</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I67" s="4" t="inlineStr">
         <is>
-          <t>When Slayer Captain enters the arena, destroy an enemy Beast character.</t>
+          <t>When Abel dies, a friendly character gains +6 Power. Exile Abel.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Slayers</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>abel.webp</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.057</t>
+          <t>N0.01.BOI.012</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Stormspear</t>
+          <t>Glorfarsall Elysium</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -4037,34 +4053,34 @@
         <v>5</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I68" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Your other characters strike with +1 Power.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Beast, Storm</t>
+          <t>Sacred Order</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>glorfarsall.webp</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.013</t>
+          <t>N0.01.BOI.091</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>The Hsal Eraklah</t>
+          <t>Norgod Reaver</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -4074,7 +4090,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Soul Elf</t>
+          <t>Norgods</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
@@ -4086,47 +4102,47 @@
         <v>14</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>2</v>
       </c>
       <c r="I69" s="4" t="inlineStr">
         <is>
-          <t>When The Hsal Eraklah enters the arena, return a character from either graveyard to your side of the arena.</t>
+          <t>Quick Attack. Strikes with +3 Power while your Citadel Mastery is below 50.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Elu-Hsal, Soul Defiler</t>
+          <t>Norgods</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>hsal-eraklah.jpg</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.11</t>
+          <t>N0.01.BOI.086</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Edmonta Lothrin</t>
+          <t>Slayer Captain</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Soul Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
@@ -4135,22 +4151,22 @@
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>6</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I70" s="4" t="inlineStr">
         <is>
-          <t>When Edmonta Lothrin enters the arena, summon 2 Rare or lower Undead characters, or 1 Epic Undead character.</t>
+          <t>When Slayer Captain enters the arena, destroy an enemy Beast character.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Elu-Hsal, Soul Defiler</t>
+          <t>Slayers</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
@@ -4163,22 +4179,22 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.01</t>
+          <t>N0.01.BOI.060</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Leon Godrick, Second Prince of the Lionheart</t>
+          <t>Stormspear</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
@@ -4187,22 +4203,22 @@
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I71" s="4" t="inlineStr">
         <is>
-          <t>Gains +2 Power for every other character in the arena.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Lionheart, Crown</t>
+          <t>Beast, Storm</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr"/>
@@ -4215,22 +4231,22 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.011</t>
+          <t>N0.01.BOI.013</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Revendrinn Nyxthorn</t>
+          <t>The Hsal Eraklah</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Soul Elf</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
@@ -4239,40 +4255,40 @@
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I72" s="4" t="inlineStr">
         <is>
-          <t>Cannot be struck the turn she enters the arena.</t>
+          <t>When The Hsal Eraklah enters the arena, return a character from either graveyard to your side of the arena.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Nyxthorn, Shadow</t>
+          <t>Elu-Hsal, Soul Defiler</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>revendrinn.webp</t>
+          <t>hsal-eraklah.jpg</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.010</t>
+          <t>N0.01.LAH.11</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Serallion, Matron of the Moon</t>
+          <t>Edmonta Lothrin</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4282,7 +4298,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Moon Elf</t>
+          <t>Soul Elf</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
@@ -4294,37 +4310,37 @@
         <v>13</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
         <is>
-          <t>When Serallion enters the arena, look at the top 3 cards of your deck and take one.</t>
+          <t>When Edmonta Lothrin enters the arena, summon 2 Rare or lower Undead characters, or 1 Epic Undead character.</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Elu-Chandra, Crown</t>
+          <t>Elu-Hsal, Soul Defiler</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>serallion.webp</t>
+          <t>edmonta-lothrin.webp</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.003</t>
+          <t>N0.01.LAH.01</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Hannarial Icetear</t>
+          <t>Leon Godrick, Second Prince of the Lionheart</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4334,105 +4350,101 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
         <is>
-          <t>When Hannarial Icetear enters the arena, summon a Red Ranger to your side of the arena.</t>
+          <t>Gains +2 Power for every other character in the arena.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Icetear</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Hannarial Icetear, Captain of the Red Rangers</t>
-        </is>
-      </c>
+          <t>Lionheart, Crown</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>hannarial-young.webp</t>
+          <t>leon-godrick.webp</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.034</t>
+          <t>N0.01.BOI.011</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Citadel Captain</t>
+          <t>Revendrinn Nyxthorn</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Human Knight</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>High Elf</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
         <is>
-          <t>While Citadel Captain is in the arena, enemy characters must strike him before your Citadel.</t>
+          <t>Cannot be struck the turn she enters the arena.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Nyxthorn, Shadow</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>revendrinn.webp</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.13</t>
+          <t>N0.01.BOI.010</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Elarien Thornwither</t>
+          <t>Serallion, Matron of the Moon</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4442,16 +4454,16 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>Rare</t>
+          <t>Moon Elf</t>
+        </is>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
+        <is>
+          <t>Epic</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G76" s="2" t="n">
         <v>5</v>
@@ -4461,40 +4473,40 @@
       </c>
       <c r="I76" s="4" t="inlineStr">
         <is>
-          <t>When Elarien Thornwither enters the arena, destroy 2 Rare or lower characters.</t>
+          <t>When Serallion enters the arena, look at the top 3 cards of your deck and take one.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Traitor</t>
+          <t>Elu-Chandra, Crown</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>serallion.webp</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.056</t>
+          <t>N0.01.BOI.003</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Mercaptain</t>
+          <t>Hannarial Icetear</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Merfolk</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
@@ -4503,40 +4515,44 @@
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
         <is>
-          <t>When Mercaptain enters the arena, return an enemy Uncommon or lower character to its owner’s hand.</t>
+          <t>When Hannarial Icetear enters the arena, summon a Red Ranger to your side of the arena.</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Sea</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr"/>
+          <t>Red Rangers, Icetear</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Hannarial Icetear, Captain of the Red Rangers</t>
+        </is>
+      </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>hannarial-young.webp</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.082</t>
+          <t>N0.01.BOI.035</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Slayer</t>
+          <t>Citadel Captain</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4546,7 +4562,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human Knight</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
@@ -4558,19 +4574,19 @@
         <v>11</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
         <is>
-          <t>Strikes with +5 Power against Beast characters.</t>
+          <t>While Citadel Captain is in the arena, enemy characters must strike him before your Citadel.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Slayers</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
@@ -4583,22 +4599,22 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.032</t>
+          <t>N0.01.LAH.13</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Bruhneville Daughter</t>
+          <t>Elarien Thornwither</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Human Spirit</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
@@ -4607,40 +4623,40 @@
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>5</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
         <is>
-          <t>Halve the Power of one enemy character for two of your opponent’s turns.</t>
+          <t>When Elarien Thornwither enters the arena, destroy 2 Rare or lower characters.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Witch</t>
+          <t>Red Rangers, Traitor</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>elarien-thornwither.webp</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.046</t>
+          <t>N0.01.BOI.059</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Goulargz</t>
+          <t>Mercaptain</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4650,7 +4666,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Merfolk</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
@@ -4659,7 +4675,7 @@
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>5</v>
@@ -4669,12 +4685,12 @@
       </c>
       <c r="I80" s="4" t="inlineStr">
         <is>
-          <t>When Goulargz enters the arena, return a Common or Uncommon character from your graveyard.</t>
+          <t>When Mercaptain enters the arena, return an enemy Uncommon or lower character to its owner’s hand.</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr"/>
@@ -4687,22 +4703,22 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.005</t>
+          <t>N0.01.BOI.085</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Hansenel Icetear</t>
+          <t>Slayer</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
@@ -4711,40 +4727,40 @@
         </is>
       </c>
       <c r="F81" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>4</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>When Hansenel Icetear enters the arena, draw a card.</t>
+          <t>Strikes with +5 Power against Beast characters.</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>Icetear</t>
+          <t>Slayers</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>hansenel.webp</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.081</t>
+          <t>N0.01.BOI.033</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Inquisitor</t>
+          <t>Bruhneville Daughter</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4754,7 +4770,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human Spirit</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
@@ -4766,37 +4782,37 @@
         <v>10</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I82" s="4" t="inlineStr">
         <is>
-          <t>When Inquisitor enters the arena, exile a card from your opponent’s graveyard.</t>
+          <t>Halve the Power of one enemy character for two of your opponent’s turns.</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
         <is>
-          <t>Inquisition</t>
+          <t>Witch</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>bruhneville-daughter.webp</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.087</t>
+          <t>N0.01.BOI.048</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Oinstan Stonewright</t>
+          <t>Goulargz</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4806,7 +4822,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Oinstans</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
@@ -4825,12 +4841,12 @@
       </c>
       <c r="I83" s="4" t="inlineStr">
         <is>
-          <t>Cannot lose more than 5 Power from a single strike.</t>
+          <t>When Goulargz enters the arena, return a Common or Uncommon character from your graveyard.</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
         <is>
-          <t>Oinstans</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr"/>
@@ -4843,12 +4859,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.016</t>
+          <t>N0.01.BOI.005</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Prince Raastali</t>
+          <t>Hansenel Icetear</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4858,7 +4874,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Half Elf Lord</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
@@ -4877,40 +4893,40 @@
       </c>
       <c r="I84" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Hansenel Icetear enters the arena, draw a card.</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dues</t>
+          <t>Icetear</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>raastali.webp</t>
+          <t>hansenel.webp</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.002</t>
+          <t>N0.01.BOI.084</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Syrel Thorneheart</t>
+          <t>Inquisitor</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
@@ -4925,44 +4941,44 @@
         <v>4</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85" s="4" t="inlineStr">
         <is>
-          <t>Strikes with +3 Power while you have another Red Ranger in the arena.</t>
+          <t>When Inquisitor enters the arena, exile a card from your opponent’s graveyard.</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Inquisition</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>syrel-thorneheart.jpg</t>
+          <t>not yet painted</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.004</t>
+          <t>N0.01.BOI.090</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Ascena Icetear</t>
+          <t>Oinstan Stonewright</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Oinstans</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
@@ -4971,22 +4987,22 @@
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I86" s="4" t="inlineStr">
         <is>
-          <t>Cannot be destroyed by a spell.</t>
+          <t>Cannot lose more than 5 Power from a single strike.</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Icetear</t>
+          <t>Oinstans</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
@@ -4999,12 +5015,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.024</t>
+          <t>N0.01.BOI.016</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Evalon, Mother of Humanity</t>
+          <t>Prince Raastali</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -5014,7 +5030,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Half Elf Lord</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
@@ -5023,7 +5039,7 @@
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>4</v>
@@ -5033,30 +5049,30 @@
       </c>
       <c r="I87" s="4" t="inlineStr">
         <is>
-          <t>At the end of your turn, restore 2 Power to each of your damaged characters.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Humanity, Healer</t>
+          <t>Elu-Dues</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>evalon.webp</t>
+          <t>raastali.webp</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.007</t>
+          <t>N0.01.BOI.002</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Fiarra</t>
+          <t>Syrel Thorneheart</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -5075,40 +5091,40 @@
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
         <is>
-          <t>When Fiarra enters the arena, give a friendly character +3 Power.</t>
+          <t>Strikes with +3 Power while you have another Red Ranger in the arena.</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>Elu Primus</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>syrel-thorneheart.jpg</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.009</t>
+          <t>N0.01.BOI.004</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Numaya Steamrose</t>
+          <t>Ascena Icetear</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -5130,19 +5146,19 @@
         <v>9</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>1</v>
       </c>
       <c r="I89" s="4" t="inlineStr">
         <is>
-          <t>Your spells cost 1 less.</t>
+          <t>Cannot be destroyed by a spell.</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Elu Primus, Artificer</t>
+          <t>Icetear</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr"/>
@@ -5155,22 +5171,22 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.03</t>
+          <t>N0.01.BOI.024</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers Squad Leader</t>
+          <t>Evalon, Mother of Humanity</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
@@ -5185,44 +5201,44 @@
         <v>4</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I90" s="4" t="inlineStr">
         <is>
-          <t>When Red Rangers Squad Leader enters the arena, summon 2 Red Rangers to your side of the arena.</t>
+          <t>At the end of your turn, restore 2 Power to each of your damaged characters.</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Humanity, Healer</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>evalon.webp</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.040</t>
+          <t>N0.01.BOI.007</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Sinodess Fleetmaster</t>
+          <t>Fiarra Starsterling</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -5237,44 +5253,44 @@
         <v>3</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
         <is>
-          <t>When Sinodess Fleetmaster enters the arena, draw a card and discard a card.</t>
+          <t>When Fiarra enters the arena, give a friendly character +3 Power.</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>Sinodess</t>
+          <t>Elu Primus</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>fiarra-starsterling.webp</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.066</t>
+          <t>N0.01.BOI.009</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
+          <t>Numaya Steamrose</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -5286,37 +5302,37 @@
         <v>9</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I92" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Your spells cost 1 less.</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Elu Primus, Artificer</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>numaya-steamrose.webp</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.080</t>
+          <t>N0.01.LAH.03</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Kalbeliya Seer</t>
+          <t>Red Rangers Squad Leader</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -5326,7 +5342,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Gypsy</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
@@ -5335,22 +5351,22 @@
         </is>
       </c>
       <c r="F93" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I93" s="4" t="inlineStr">
         <is>
-          <t>When Kalbeliya Seer enters the arena, look at the top 3 cards of your deck and reorder them.</t>
+          <t>When Red Rangers Squad Leader enters the arena, summon 2 Red Rangers to your side of the arena.</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>Five Tribes</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
@@ -5363,22 +5379,22 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.008</t>
+          <t>N0.01.BOI.042</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Mayra Padukindel</t>
+          <t>Sinodess Fleetmaster</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -5387,22 +5403,22 @@
         </is>
       </c>
       <c r="F94" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" s="4" t="inlineStr">
         <is>
-          <t>When Mayra Padukindel enters the arena, draw a card.</t>
+          <t>When Sinodess Fleetmaster enters the arena, draw a card and discard a card.</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>Elu Primus</t>
+          <t>Sinodess</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
@@ -5415,22 +5431,22 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.12</t>
+          <t>N0.01.BOI.069</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Rellien &amp; Vessa Aerwyn</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Legendary Character</t>
+          <t>Character</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -5439,22 +5455,22 @@
         </is>
       </c>
       <c r="F95" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" s="4" t="inlineStr">
         <is>
-          <t>May strike twice in the same turn.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers, Twins</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
@@ -5467,12 +5483,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.123</t>
+          <t>N0.01.BOI.083</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Cliff Garuda</t>
+          <t>Kalbeliya Seer</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -5482,16 +5498,16 @@
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+          <t>Gypsy</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F96" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>3</v>
@@ -5501,12 +5517,12 @@
       </c>
       <c r="I96" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Kalbeliya Seer enters the arena, look at the top 3 cards of your deck and reorder them.</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>Beast, Sky</t>
+          <t>Five Tribes</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
@@ -5519,46 +5535,46 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.121</t>
+          <t>N0.01.BOI.008</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Dragon Elf Outrider</t>
+          <t>Mayra Padukindel</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Dragon Elf</t>
-        </is>
-      </c>
-      <c r="E97" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+          <t>High Elf</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F97" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>3</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I97" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Mayra Padukindel enters the arena, draw a card.</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dragar</t>
+          <t>Elu Primus</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
@@ -5571,64 +5587,64 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.122</t>
+          <t>N0.01.LAH.12</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Dwarf Stoneguard</t>
+          <t>Rellien &amp; Vessa Aerwyn</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Character</t>
+          <t>Legendary Character</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Dwarf</t>
-        </is>
-      </c>
-      <c r="E98" s="8" t="inlineStr">
-        <is>
-          <t>Uncommon</t>
+          <t>High Elf</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>Rare</t>
         </is>
       </c>
       <c r="F98" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G98" s="2" t="n">
         <v>4</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I98" s="4" t="inlineStr">
         <is>
-          <t>Cannot be destroyed by a spell.</t>
+          <t>May strike twice in the same turn.</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>Dwarf</t>
+          <t>Red Rangers, Twins</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>not yet painted</t>
+          <t>rellien-and-vessa.webp</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.124</t>
+          <t>N0.01.BOI.126</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood Initiate</t>
+          <t>Cliff Garuda</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -5638,7 +5654,7 @@
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
@@ -5657,12 +5673,12 @@
       </c>
       <c r="I99" s="4" t="inlineStr">
         <is>
-          <t>When Gods Blood Initiate enters the arena, look at your opponent’s hand.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>Gods Blood</t>
+          <t>Beast, Sky</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr"/>
@@ -5675,12 +5691,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.120</t>
+          <t>N0.01.BOI.124</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Icetear Winterguard</t>
+          <t>Dragon Elf Outrider</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -5690,7 +5706,7 @@
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Dragon Elf</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
@@ -5702,19 +5718,19 @@
         <v>7</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I100" s="4" t="inlineStr">
         <is>
-          <t>While Icetear Winterguard is in the arena, enemy characters must strike her before your Citadel.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
         <is>
-          <t>Icetear</t>
+          <t>Elu-Dragar</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr"/>
@@ -5727,12 +5743,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.118</t>
+          <t>N0.01.BOI.125</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Hedge Witch</t>
+          <t>Dwarf Stoneguard</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -5742,7 +5758,7 @@
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Dwarf</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
@@ -5751,22 +5767,22 @@
         </is>
       </c>
       <c r="F101" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I101" s="4" t="inlineStr">
         <is>
-          <t>When Hedge Witch enters the arena, an enemy character loses 4 Power for one turn.</t>
+          <t>Cannot be destroyed by a spell.</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Witch</t>
+          <t>Dwarf</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr"/>
@@ -5779,12 +5795,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.114</t>
+          <t>N0.01.BOI.127</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Inquisition Warden</t>
+          <t>Gods Blood Initiate</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -5794,7 +5810,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Gods Blood</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
@@ -5803,7 +5819,7 @@
         </is>
       </c>
       <c r="F102" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>3</v>
@@ -5813,12 +5829,12 @@
       </c>
       <c r="I102" s="4" t="inlineStr">
         <is>
-          <t>Enemy spells cost 1 more while Inquisition Warden is in the arena.</t>
+          <t>When Gods Blood Initiate enters the arena, look at your opponent’s hand.</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>Inquisition</t>
+          <t>Gods Blood</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr"/>
@@ -5831,12 +5847,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.079</t>
+          <t>N0.01.BOI.123</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Kalbeliya Dancer</t>
+          <t>Icetear Winterguard</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -5846,7 +5862,7 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Gypsy</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
@@ -5855,22 +5871,22 @@
         </is>
       </c>
       <c r="F103" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I103" s="4" t="inlineStr">
         <is>
-          <t>When Kalbeliya Dancer enters the arena, an enemy character cannot strike next turn.</t>
+          <t>While Icetear Winterguard is in the arena, enemy characters must strike her before your Citadel.</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>Five Tribes</t>
+          <t>Icetear</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr"/>
@@ -5883,12 +5899,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.053</t>
+          <t>N0.01.BOI.121</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Mersoldier</t>
+          <t>Hedge Witch</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -5898,7 +5914,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Merfolk</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
@@ -5915,10 +5931,14 @@
       <c r="H104" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I104" s="4" t="inlineStr"/>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>When Hedge Witch enters the arena, an enemy character loses 4 Power for one turn.</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Witch</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr"/>
@@ -5931,12 +5951,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.112</t>
+          <t>N0.01.BOI.117</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Moon Elf Tidecaller</t>
+          <t>Inquisition Warden</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -5946,7 +5966,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Moon Elf</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
@@ -5958,19 +5978,19 @@
         <v>6</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I105" s="4" t="inlineStr">
         <is>
-          <t>When Moon Elf Tidecaller enters the arena, an enemy character loses 3 Power.</t>
+          <t>Enemy spells cost 1 more while Inquisition Warden is in the arena.</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr">
         <is>
-          <t>Elu-Chandra, Sea</t>
+          <t>Inquisition</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr"/>
@@ -5983,12 +6003,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.117</t>
+          <t>N0.01.BOI.082</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Norgod Oarsman</t>
+          <t>Kalbeliya Dancer</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -5998,7 +6018,7 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Norgods</t>
+          <t>Gypsy</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
@@ -6010,19 +6030,19 @@
         <v>6</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I106" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Kalbeliya Dancer enters the arena, an enemy character cannot strike next turn.</t>
         </is>
       </c>
       <c r="J106" s="2" t="inlineStr">
         <is>
-          <t>Norgods</t>
+          <t>Five Tribes</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr"/>
@@ -6035,12 +6055,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.119</t>
+          <t>N0.01.BOI.056</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers Tracker</t>
+          <t>Mersoldier</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -6050,7 +6070,7 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Merfolk</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
@@ -6067,14 +6087,10 @@
       <c r="H107" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I107" s="4" t="inlineStr">
-        <is>
-          <t>Counts as a Red Ranger. When Red Rangers Tracker enters the arena, look at the top 2 cards of your deck.</t>
-        </is>
-      </c>
+      <c r="I107" s="4" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr"/>
@@ -6087,12 +6103,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.14</t>
+          <t>N0.01.BOI.115</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers Warrior</t>
+          <t>Moon Elf Tidecaller</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -6102,7 +6118,7 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Moon Elf</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
@@ -6114,19 +6130,19 @@
         <v>6</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I108" s="4" t="inlineStr">
         <is>
-          <t>When Red Rangers Warrior dies, she returns to your side of the arena with 1 Power at the start of your opponent’s turn. If she dies again, exile her.</t>
+          <t>When Moon Elf Tidecaller enters the arena, an enemy character loses 3 Power.</t>
         </is>
       </c>
       <c r="J108" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Elu-Chandra, Sea</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr"/>
@@ -6139,12 +6155,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.116</t>
+          <t>N0.01.BOI.120</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Reef Lurker</t>
+          <t>Norgod Oarsman</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -6154,7 +6170,7 @@
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Merfolk</t>
+          <t>Norgods</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
@@ -6173,12 +6189,12 @@
       </c>
       <c r="I109" s="4" t="inlineStr">
         <is>
-          <t>Cannot be struck the turn it enters the arena.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J109" s="2" t="inlineStr">
         <is>
-          <t>Sea</t>
+          <t>Norgods</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr"/>
@@ -6191,12 +6207,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.115</t>
+          <t>N0.01.BOI.122</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Sinodess Corsair</t>
+          <t>Red Rangers Tracker</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -6206,7 +6222,7 @@
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
@@ -6225,12 +6241,12 @@
       </c>
       <c r="I110" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Counts as a Red Ranger. When Red Rangers Tracker enters the arena, look at the top 2 cards of your deck.</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr">
         <is>
-          <t>Sinodess</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr"/>
@@ -6243,12 +6259,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.078</t>
+          <t>N0.01.LAH.14</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Sister of the Moon</t>
+          <t>Red Rangers Warrior</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -6258,7 +6274,7 @@
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Human Knight</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
@@ -6270,19 +6286,19 @@
         <v>6</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I111" s="4" t="inlineStr">
         <is>
-          <t>Strikes with +2 Power on your opponent’s turn.</t>
+          <t>When Red Rangers Warrior dies, she returns to your side of the arena with 1 Power at the start of your opponent’s turn. If she dies again, exile her.</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Knight Sisterhood, Knight</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr"/>
@@ -6295,12 +6311,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.113</t>
+          <t>N0.01.BOI.119</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Soul Elf Acolyte</t>
+          <t>Reef Lurker</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -6310,7 +6326,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Soul Elf</t>
+          <t>Merfolk</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
@@ -6329,12 +6345,12 @@
       </c>
       <c r="I112" s="4" t="inlineStr">
         <is>
-          <t>When Soul Elf Acolyte enters the arena, return a Common character from your graveyard.</t>
+          <t>Cannot be struck the turn it enters the arena.</t>
         </is>
       </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
-          <t>Elu-Hsal, Soul Defiler</t>
+          <t>Sea</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr"/>
@@ -6347,12 +6363,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.109</t>
+          <t>N0.01.BOI.118</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Bone Picker</t>
+          <t>Sinodess Corsair</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -6362,7 +6378,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
@@ -6371,7 +6387,7 @@
         </is>
       </c>
       <c r="F113" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>2</v>
@@ -6381,12 +6397,12 @@
       </c>
       <c r="I113" s="4" t="inlineStr">
         <is>
-          <t>When Bone Picker enters the arena, exile a card from a graveyard.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Sinodess</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr"/>
@@ -6399,12 +6415,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.086</t>
+          <t>N0.01.BOI.081</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Exodan Wanderer</t>
+          <t>Sister of the Moon</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -6414,7 +6430,7 @@
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Exodas</t>
+          <t>Human Knight</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
@@ -6423,7 +6439,7 @@
         </is>
       </c>
       <c r="F114" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>2</v>
@@ -6433,12 +6449,12 @@
       </c>
       <c r="I114" s="4" t="inlineStr">
         <is>
-          <t>When Exodan Wanderer enters the arena, draw a card if you have no other character.</t>
+          <t>Strikes with +2 Power on your opponent’s turn.</t>
         </is>
       </c>
       <c r="J114" s="2" t="inlineStr">
         <is>
-          <t>Exodas</t>
+          <t>Knight Sisterhood, Knight</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr"/>
@@ -6451,12 +6467,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.052</t>
+          <t>N0.01.BOI.116</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Garudling</t>
+          <t>Soul Elf Acolyte</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -6466,7 +6482,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Soul Elf</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
@@ -6475,7 +6491,7 @@
         </is>
       </c>
       <c r="F115" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G115" s="2" t="n">
         <v>2</v>
@@ -6485,12 +6501,12 @@
       </c>
       <c r="I115" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Soul Elf Acolyte enters the arena, return a Common character from your graveyard.</t>
         </is>
       </c>
       <c r="J115" s="2" t="inlineStr">
         <is>
-          <t>Beast, Sky</t>
+          <t>Elu-Hsal, Soul Defiler</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr"/>
@@ -6503,12 +6519,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.106</t>
+          <t>N0.01.BOI.112</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Kingdom Militia</t>
+          <t>Bone Picker</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -6518,7 +6534,7 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
@@ -6535,10 +6551,14 @@
       <c r="H116" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I116" s="4" t="inlineStr"/>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>When Bone Picker enters the arena, exile a card from a graveyard.</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr"/>
@@ -6551,12 +6571,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.110</t>
+          <t>N0.01.BOI.089</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Magi Apprentice</t>
+          <t>Exodan Wanderer</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -6566,7 +6586,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Human Wizard</t>
+          <t>Exodas</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
@@ -6578,19 +6598,19 @@
         <v>5</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I117" s="4" t="inlineStr">
         <is>
-          <t>When Magi Apprentice enters the arena, draw a spell from the top 4 cards of your deck.</t>
+          <t>When Exodan Wanderer enters the arena, draw a card if you have no other character.</t>
         </is>
       </c>
       <c r="J117" s="2" t="inlineStr">
         <is>
-          <t>Archmagi</t>
+          <t>Exodas</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr"/>
@@ -6603,12 +6623,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.17</t>
+          <t>N0.01.BOI.055</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Moon Warrior</t>
+          <t>Garudling</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -6618,7 +6638,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
@@ -6635,10 +6655,14 @@
       <c r="H118" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I118" s="4" t="inlineStr"/>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>Quick Attack.</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Beast, Sky</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr"/>
@@ -6651,12 +6675,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.111</t>
+          <t>N0.01.BOI.109</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Oinstan Mason</t>
+          <t>Kingdom Militia</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -6666,7 +6690,7 @@
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Oinstans</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
@@ -6683,14 +6707,10 @@
       <c r="H119" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I119" s="4" t="inlineStr">
-        <is>
-          <t>Cannot lose more than 3 Power from a single strike.</t>
-        </is>
-      </c>
+      <c r="I119" s="4" t="inlineStr"/>
       <c r="J119" s="2" t="inlineStr">
         <is>
-          <t>Oinstans</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr"/>
@@ -6703,12 +6723,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.108</t>
+          <t>N0.01.BOI.113</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Orc Skirmisher</t>
+          <t>Magi Apprentice</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -6718,7 +6738,7 @@
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Orc</t>
+          <t>Human Wizard</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
@@ -6730,19 +6750,19 @@
         <v>5</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>3</v>
       </c>
       <c r="I120" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Magi Apprentice enters the arena, draw a spell from the top 4 cards of your deck.</t>
         </is>
       </c>
       <c r="J120" s="2" t="inlineStr">
         <is>
-          <t>Orc, Warband</t>
+          <t>Archmagi</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr"/>
@@ -6755,12 +6775,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>N0.01.LAH.05</t>
+          <t>N0.01.LAH.17</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers Archer</t>
+          <t>Moon Warrior</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -6787,11 +6807,7 @@
       <c r="H121" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I121" s="4" t="inlineStr">
-        <is>
-          <t>Strikes with +2 Power against a Rare or higher character.</t>
-        </is>
-      </c>
+      <c r="I121" s="4" t="inlineStr"/>
       <c r="J121" s="2" t="inlineStr">
         <is>
           <t>Red Rangers</t>
@@ -6807,12 +6823,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.107</t>
+          <t>N0.01.BOI.114</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Slayer Apprentice</t>
+          <t>Oinstan Mason</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -6822,7 +6838,7 @@
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Oinstans</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
@@ -6841,12 +6857,12 @@
       </c>
       <c r="I122" s="4" t="inlineStr">
         <is>
-          <t>Strikes with +3 Power against Beast characters.</t>
+          <t>Cannot lose more than 3 Power from a single strike.</t>
         </is>
       </c>
       <c r="J122" s="2" t="inlineStr">
         <is>
-          <t>Slayers</t>
+          <t>Oinstans</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr"/>
@@ -6859,12 +6875,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.074</t>
+          <t>N0.01.BOI.111</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Orc Skirmisher</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -6874,16 +6890,16 @@
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Demon</t>
-        </is>
-      </c>
-      <c r="E123" s="9" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>Orc</t>
+        </is>
+      </c>
+      <c r="E123" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F123" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>2</v>
@@ -6898,7 +6914,7 @@
       </c>
       <c r="J123" s="2" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Orc, Warband</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr"/>
@@ -6911,12 +6927,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.104</t>
+          <t>N0.01.LAH.05</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Kalbeliya Outrider</t>
+          <t>Red Rangers Archer</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -6926,16 +6942,16 @@
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Gypsy</t>
-        </is>
-      </c>
-      <c r="E124" s="9" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>High Elf</t>
+        </is>
+      </c>
+      <c r="E124" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F124" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G124" s="2" t="n">
         <v>2</v>
@@ -6945,12 +6961,12 @@
       </c>
       <c r="I124" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Strikes with +2 Power against a Rare or higher character.</t>
         </is>
       </c>
       <c r="J124" s="2" t="inlineStr">
         <is>
-          <t>Five Tribes</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr"/>
@@ -6963,12 +6979,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.033</t>
+          <t>N0.01.BOI.110</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Slayer Apprentice</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -6978,16 +6994,16 @@
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Human Knight</t>
-        </is>
-      </c>
-      <c r="E125" s="9" t="inlineStr">
-        <is>
-          <t>Common</t>
+          <t>Human</t>
+        </is>
+      </c>
+      <c r="E125" s="8" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="F125" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>2</v>
@@ -6995,10 +7011,14 @@
       <c r="H125" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I125" s="4" t="inlineStr"/>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>Strikes with +3 Power against Beast characters.</t>
+        </is>
+      </c>
       <c r="J125" s="2" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Slayers</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr"/>
@@ -7011,12 +7031,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.038</t>
+          <t>N0.01.BOI.077</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Orc Raider</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -7026,7 +7046,7 @@
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Orc</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="E126" s="9" t="inlineStr">
@@ -7050,7 +7070,7 @@
       </c>
       <c r="J126" s="2" t="inlineStr">
         <is>
-          <t>Orc, Warband</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr"/>
@@ -7063,12 +7083,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.105</t>
+          <t>N0.01.BOI.107</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers Scout</t>
+          <t>Kalbeliya Outrider</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -7078,7 +7098,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Gypsy</t>
         </is>
       </c>
       <c r="E127" s="9" t="inlineStr">
@@ -7097,12 +7117,12 @@
       </c>
       <c r="I127" s="4" t="inlineStr">
         <is>
-          <t>Counts as a Red Ranger.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Five Tribes</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr"/>
@@ -7115,12 +7135,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.103</t>
+          <t>N0.01.BOI.034</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Spearman of Adamas</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -7130,7 +7150,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Human Knight</t>
         </is>
       </c>
       <c r="E128" s="9" t="inlineStr">
@@ -7150,7 +7170,7 @@
       <c r="I128" s="4" t="inlineStr"/>
       <c r="J128" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr"/>
@@ -7163,12 +7183,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.102</t>
+          <t>N0.01.BOI.040</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Treant Sapling</t>
+          <t>Orc Raider</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -7178,7 +7198,7 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Treant</t>
+          <t>Orc</t>
         </is>
       </c>
       <c r="E129" s="9" t="inlineStr">
@@ -7197,12 +7217,12 @@
       </c>
       <c r="I129" s="4" t="inlineStr">
         <is>
-          <t>At the end of your turn, Treant Sapling gains 1 Power.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J129" s="2" t="inlineStr">
         <is>
-          <t>Treant</t>
+          <t>Orc, Warband</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr"/>
@@ -7215,12 +7235,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.101</t>
+          <t>N0.01.BOI.108</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>Tylon Whelp</t>
+          <t>Red Rangers Scout</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -7230,7 +7250,7 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Tylon</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E130" s="9" t="inlineStr">
@@ -7249,12 +7269,12 @@
       </c>
       <c r="I130" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>Counts as a Red Ranger.</t>
         </is>
       </c>
       <c r="J130" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr"/>
@@ -7267,12 +7287,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.100</t>
+          <t>N0.01.BOI.106</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>Abyssal Insect</t>
+          <t>Spearman of Adamas</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -7282,7 +7302,7 @@
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Insect</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E131" s="9" t="inlineStr">
@@ -7291,10 +7311,10 @@
         </is>
       </c>
       <c r="F131" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>3</v>
@@ -7302,7 +7322,7 @@
       <c r="I131" s="4" t="inlineStr"/>
       <c r="J131" s="2" t="inlineStr">
         <is>
-          <t>Corrupted</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr"/>
@@ -7315,12 +7335,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.054</t>
+          <t>N0.01.BOI.105</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Beastling</t>
+          <t>Treant Sapling</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -7330,7 +7350,7 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Treant</t>
         </is>
       </c>
       <c r="E132" s="9" t="inlineStr">
@@ -7339,18 +7359,22 @@
         </is>
       </c>
       <c r="F132" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I132" s="4" t="inlineStr"/>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>At the end of your turn, Treant Sapling gains 1 Power.</t>
+        </is>
+      </c>
       <c r="J132" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Treant</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr"/>
@@ -7363,12 +7387,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.095</t>
+          <t>N0.01.BOI.104</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Elu Primus Initiate</t>
+          <t>Tylon Whelp</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -7378,7 +7402,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>High Elf</t>
+          <t>Tylon</t>
         </is>
       </c>
       <c r="E133" s="9" t="inlineStr">
@@ -7387,18 +7411,22 @@
         </is>
       </c>
       <c r="F133" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I133" s="4" t="inlineStr"/>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>Quick Attack.</t>
+        </is>
+      </c>
       <c r="J133" s="2" t="inlineStr">
         <is>
-          <t>Elu Primus</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr"/>
@@ -7411,12 +7439,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.099</t>
+          <t>N0.01.BOI.103</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Exodan Scout</t>
+          <t>Abyssal Insect</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -7426,7 +7454,7 @@
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Exodas</t>
+          <t>Insect</t>
         </is>
       </c>
       <c r="E134" s="9" t="inlineStr">
@@ -7443,14 +7471,10 @@
       <c r="H134" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I134" s="4" t="inlineStr">
-        <is>
-          <t>Quick Attack.</t>
-        </is>
-      </c>
+      <c r="I134" s="4" t="inlineStr"/>
       <c r="J134" s="2" t="inlineStr">
         <is>
-          <t>Exodas</t>
+          <t>Corrupted</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr"/>
@@ -7463,12 +7487,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.045</t>
+          <t>N0.01.BOI.057</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Ghoul</t>
+          <t>Beastling</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -7478,7 +7502,7 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="E135" s="9" t="inlineStr">
@@ -7498,7 +7522,7 @@
       <c r="I135" s="4" t="inlineStr"/>
       <c r="J135" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr"/>
@@ -7511,12 +7535,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.094</t>
+          <t>N0.01.BOI.098</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Icetear Squire</t>
+          <t>Elu Primus Initiate</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -7543,14 +7567,10 @@
       <c r="H136" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I136" s="4" t="inlineStr">
-        <is>
-          <t>When Icetear Squire enters the arena, give a friendly Icetear character +2 Power.</t>
-        </is>
-      </c>
+      <c r="I136" s="4" t="inlineStr"/>
       <c r="J136" s="2" t="inlineStr">
         <is>
-          <t>Icetear</t>
+          <t>Elu Primus</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr"/>
@@ -7563,12 +7583,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.051</t>
+          <t>N0.01.BOI.102</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Imptizzle</t>
+          <t>Exodan Scout</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -7578,7 +7598,7 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Imp</t>
+          <t>Exodas</t>
         </is>
       </c>
       <c r="E137" s="9" t="inlineStr">
@@ -7597,12 +7617,12 @@
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>When Imptizzle dies, draw a card.</t>
+          <t>Quick Attack.</t>
         </is>
       </c>
       <c r="J137" s="2" t="inlineStr">
         <is>
-          <t>Demon</t>
+          <t>Exodas</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr"/>
@@ -7615,12 +7635,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.097</t>
+          <t>N0.01.BOI.047</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Novice of the Moon</t>
+          <t>Ghoul</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -7630,7 +7650,7 @@
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Human Knight</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="E138" s="9" t="inlineStr">
@@ -7650,7 +7670,7 @@
       <c r="I138" s="4" t="inlineStr"/>
       <c r="J138" s="2" t="inlineStr">
         <is>
-          <t>Knight Sisterhood, Knight</t>
+          <t>Undead</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr"/>
@@ -7663,12 +7683,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.001</t>
+          <t>N0.01.BOI.097</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Red Ranger</t>
+          <t>Icetear Squire</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -7695,10 +7715,14 @@
       <c r="H139" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I139" s="4" t="inlineStr"/>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>When Icetear Squire enters the arena, give a friendly Icetear character +2 Power.</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="inlineStr">
         <is>
-          <t>Red Rangers</t>
+          <t>Icetear</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr"/>
@@ -7711,12 +7735,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.098</t>
+          <t>N0.01.BOI.054</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Sinodess Deckhand</t>
+          <t>Imptizzle</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -7726,7 +7750,7 @@
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Human</t>
+          <t>Imp</t>
         </is>
       </c>
       <c r="E140" s="9" t="inlineStr">
@@ -7745,12 +7769,12 @@
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>When Sinodess Deckhand enters the arena, draw a card if your Citadel Mastery is below 50.</t>
+          <t>When Imptizzle dies, draw a card.</t>
         </is>
       </c>
       <c r="J140" s="2" t="inlineStr">
         <is>
-          <t>Sinodess</t>
+          <t>Demon</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr"/>
@@ -7763,12 +7787,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.096</t>
+          <t>N0.01.BOI.100</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Squire of the Citadel</t>
+          <t>Novice of the Moon</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -7795,14 +7819,10 @@
       <c r="H141" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I141" s="4" t="inlineStr">
-        <is>
-          <t>When Squire of the Citadel enters the arena, give a friendly Knight +2 Power.</t>
-        </is>
-      </c>
+      <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="2" t="inlineStr">
         <is>
-          <t>Knight</t>
+          <t>Knight Sisterhood, Knight</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr"/>
@@ -7815,12 +7835,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.055</t>
+          <t>N0.01.BOI.001</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Wolf</t>
+          <t>Red Ranger</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -7830,7 +7850,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>High Elf</t>
         </is>
       </c>
       <c r="E142" s="9" t="inlineStr">
@@ -7850,7 +7870,7 @@
       <c r="I142" s="4" t="inlineStr"/>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Beast, Wolf</t>
+          <t>Red Rangers</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr"/>
@@ -7863,12 +7883,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.090</t>
+          <t>N0.01.BOI.101</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Enclave Farmer</t>
+          <t>Sinodess Deckhand</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -7887,7 +7907,7 @@
         </is>
       </c>
       <c r="F143" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>1</v>
@@ -7897,12 +7917,12 @@
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>When Enclave Farmer dies, restore 3 Citadel Mastery.</t>
+          <t>When Sinodess Deckhand enters the arena, draw a card if your Citadel Mastery is below 50.</t>
         </is>
       </c>
       <c r="J143" s="2" t="inlineStr">
         <is>
-          <t>Humanity</t>
+          <t>Sinodess</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr"/>
@@ -7915,12 +7935,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.091</t>
+          <t>N0.01.BOI.099</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Half Elf Levy</t>
+          <t>Squire of the Citadel</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -7930,7 +7950,7 @@
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Half Elf</t>
+          <t>Human Knight</t>
         </is>
       </c>
       <c r="E144" s="9" t="inlineStr">
@@ -7939,7 +7959,7 @@
         </is>
       </c>
       <c r="F144" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>1</v>
@@ -7947,10 +7967,14 @@
       <c r="H144" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>When Squire of the Citadel enters the arena, give a friendly Knight +2 Power.</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="inlineStr">
         <is>
-          <t>Elu-Dues</t>
+          <t>Knight</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr"/>
@@ -7963,12 +7987,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.092</t>
+          <t>N0.01.BOI.058</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Risen Levy</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -7978,7 +8002,7 @@
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Beast</t>
         </is>
       </c>
       <c r="E145" s="9" t="inlineStr">
@@ -7987,7 +8011,7 @@
         </is>
       </c>
       <c r="F145" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>1</v>
@@ -7995,14 +8019,10 @@
       <c r="H145" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="I145" s="4" t="inlineStr">
-        <is>
-          <t>When Risen Levy dies, summon a Ghoul.</t>
-        </is>
-      </c>
+      <c r="I145" s="4" t="inlineStr"/>
       <c r="J145" s="2" t="inlineStr">
         <is>
-          <t>Undead</t>
+          <t>Beast, Wolf</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr"/>
@@ -8020,7 +8040,7 @@
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Serpent Hatchling</t>
+          <t>Enclave Farmer</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -8030,7 +8050,7 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Beast</t>
+          <t>Human</t>
         </is>
       </c>
       <c r="E146" s="9" t="inlineStr">
@@ -8049,12 +8069,12 @@
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>Quick Attack.</t>
+          <t>When Enclave Farmer dies, restore 3 Citadel Mastery.</t>
         </is>
       </c>
       <c r="J146" s="2" t="inlineStr">
         <is>
-          <t>Beast, Corrupted</t>
+          <t>Humanity</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr"/>
@@ -8064,8 +8084,160 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>N0.01.BOI.094</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Half Elf Levy</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Half Elf</t>
+        </is>
+      </c>
+      <c r="E147" s="9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I147" s="4" t="inlineStr"/>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Elu-Dues</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>not yet painted</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>N0.01.BOI.095</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Risen Levy</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
+      </c>
+      <c r="E148" s="9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>When Risen Levy dies, summon a Ghoul.</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr">
+        <is>
+          <t>Undead</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>not yet painted</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>N0.01.BOI.096</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Serpent Hatchling</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Character</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Beast</t>
+        </is>
+      </c>
+      <c r="E149" s="9" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>Quick Attack.</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>Beast, Corrupted</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>not yet painted</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L146"/>
+  <autoFilter ref="A1:L149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8204,7 +8376,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.159</t>
+          <t>N0.01.BOI.162</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -8250,7 +8422,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.149</t>
+          <t>N0.01.BOI.152</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -8296,7 +8468,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.147</t>
+          <t>N0.01.BOI.150</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -8338,7 +8510,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.148</t>
+          <t>N0.01.BOI.151</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -8384,7 +8556,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.158</t>
+          <t>N0.01.BOI.161</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -8430,7 +8602,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.144</t>
+          <t>N0.01.BOI.147</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -8518,7 +8690,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.137</t>
+          <t>N0.01.BOI.140</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -8564,7 +8736,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.146</t>
+          <t>N0.01.BOI.149</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -8610,7 +8782,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.155</t>
+          <t>N0.01.BOI.158</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -8656,7 +8828,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.145</t>
+          <t>N0.01.BOI.148</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -8702,7 +8874,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.156</t>
+          <t>N0.01.BOI.159</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -8748,7 +8920,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.157</t>
+          <t>N0.01.BOI.160</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -8794,7 +8966,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.138</t>
+          <t>N0.01.BOI.141</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -8840,7 +9012,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.136</t>
+          <t>N0.01.BOI.139</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -8886,7 +9058,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.130</t>
+          <t>N0.01.BOI.133</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -8932,7 +9104,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.152</t>
+          <t>N0.01.BOI.155</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -8978,7 +9150,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.134</t>
+          <t>N0.01.BOI.137</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -9024,7 +9196,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.135</t>
+          <t>N0.01.BOI.138</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -9070,7 +9242,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.142</t>
+          <t>N0.01.BOI.145</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -9116,7 +9288,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.143</t>
+          <t>N0.01.BOI.146</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -9200,7 +9372,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.131</t>
+          <t>N0.01.BOI.134</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -9246,7 +9418,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.151</t>
+          <t>N0.01.BOI.154</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -9292,7 +9464,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.133</t>
+          <t>N0.01.BOI.136</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -9338,7 +9510,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.153</t>
+          <t>N0.01.BOI.156</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -9384,7 +9556,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.154</t>
+          <t>N0.01.BOI.157</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -9430,7 +9602,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.141</t>
+          <t>N0.01.BOI.144</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -9476,7 +9648,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.129</t>
+          <t>N0.01.BOI.132</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -9522,7 +9694,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.132</t>
+          <t>N0.01.BOI.135</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -9568,7 +9740,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.127</t>
+          <t>N0.01.BOI.130</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -9614,7 +9786,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.128</t>
+          <t>N0.01.BOI.131</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -9660,7 +9832,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.139</t>
+          <t>N0.01.BOI.142</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -9706,7 +9878,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.140</t>
+          <t>N0.01.BOI.143</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -9748,7 +9920,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.126</t>
+          <t>N0.01.BOI.129</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -9794,7 +9966,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.150</t>
+          <t>N0.01.BOI.153</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -9840,7 +10012,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>N0.01.BOI.125</t>
+          <t>N0.01.BOI.128</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -10055,7 +10227,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
@@ -10079,7 +10251,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/docs/blood-of-icetear-cards.xlsx
+++ b/docs/blood-of-icetear-cards.xlsx
@@ -720,7 +720,7 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>corrupted-angel.webp</t>
+          <t>devil-kings-avatar.webp</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>golden-angel.webp</t>
+          <t>archangel-skyrehaal.webp</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>morrigan.jpg</t>
+          <t>morrigan-avatar.webp</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>sinbad-sinodess.jpg</t>
+          <t>sinbad-sinodess.webp</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lucifials-avatar.jpg</t>
+          <t>whisperer.webp</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>spider-horror.webp</t>
+          <t>barlgowrath.webp</t>
         </is>
       </c>
     </row>
